--- a/配置表格/H幻化配置表.xlsx
+++ b/配置表格/H幻化配置表.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="cosmetic_config" sheetId="1" r:id="rId1"/>
+    <sheet name="本轮配置说明" sheetId="2" r:id="rIdConfig2"/>
+    <sheet name="本轮资源需求" sheetId="3" r:id="rIdConfig3"/>
   </sheets>
   <calcPr calcId="191029" calcCompleted="0" calcOnSave="0"/>
   <extLst>
@@ -216,7 +218,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -385,8 +387,50 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -591,8 +635,41 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -698,8 +775,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -848,8 +946,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="9"/>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="10"/>
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="11"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -862,6 +963,39 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="9" xfId="50"/>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="9" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="9" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="9" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="9" xfId="50" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="10" xfId="51"/>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="10" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="10" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="10" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="10" xfId="51" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="11" xfId="52"/>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="11" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="11" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="11" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="43" borderId="11" xfId="52" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1344,7 +1478,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1420,6 +1554,11 @@
       <c r="V1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gender</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:22">
       <c r="A2" s="1" t="s">
@@ -1471,6 +1610,11 @@
       </c>
       <c r="V2" s="1" t="s">
         <v>17</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">string#regex=^(通用|男|女)$</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:22">
@@ -1512,6 +1656,11 @@
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="4" ht="26" customHeight="1" spans="1:22">
       <c r="A4" s="2" t="s">
@@ -1580,206 +1729,676 @@
       <c r="V4" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">适用性别（通用/男/女；默认=通用）</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:22">
       <c r="A5" s="3"/>
-      <c r="B5" s="3">
+      <c r="B5" t="n" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="C5" t="str" s="3">
+        <v>岱舆纪行</v>
+      </c>
+      <c r="D5" t="str" s="3">
+        <v>头像</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" t="str" s="4">
+        <v>清影入画，留一缕仙姿于方寸之间。</v>
+      </c>
+      <c r="H5" t="str" s="4">
+        <v>完成支线“踏查·垂练岩”获得激活道具</v>
+      </c>
+      <c r="I5" t="n" s="3">
         <v>12904000</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="3">
-        <v>12904000</v>
-      </c>
-      <c r="J5" s="3">
+      <c r="J5" t="n" s="3">
         <v>1</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
-      <c r="N5" s="3">
+      <c r="N5" t="n" s="3">
         <v>10000</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P5" s="3">
-        <v>80</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R5" s="3">
-        <v>100</v>
+      <c r="O5" t="str" s="3">
+        <v>生命值</v>
+      </c>
+      <c r="P5" t="n" s="3">
+        <v>20</v>
+      </c>
+      <c r="Q5" t="str" s="3">
+        <v>基础修为增幅</v>
+      </c>
+      <c r="R5" t="n" s="3">
+        <v>25</v>
       </c>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通用</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="64" customHeight="1" spans="1:22">
       <c r="A6" s="3"/>
-      <c r="B6" s="3">
+      <c r="B6" t="n" s="3">
         <v>101</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="C6" t="str" s="3">
+        <v>太虚问道</v>
+      </c>
+      <c r="D6" t="str" s="3">
+        <v>称号</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" t="str" s="4">
+        <v>以道为名，映照修行之志。</v>
+      </c>
+      <c r="H6" t="str" s="4">
+        <v>完成大乘主线“回望所来”获得激活道具</v>
+      </c>
+      <c r="I6" t="n" s="3">
         <v>12904001</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="3">
-        <v>12904001</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="J6" t="n" s="3">
         <v>1</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3">
+      <c r="M6" t="str" s="3">
+        <v>overhead</v>
+      </c>
+      <c r="N6" t="n" s="3">
         <v>10000</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P6" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R6" s="3">
-        <v>100</v>
+      <c r="O6" t="str" s="3">
+        <v>生命值</v>
+      </c>
+      <c r="P6" t="n" s="3">
+        <v>20</v>
+      </c>
+      <c r="Q6" t="str" s="3">
+        <v>基础修为增幅</v>
+      </c>
+      <c r="R6" t="n" s="3">
+        <v>25</v>
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通用</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="64" customHeight="1" spans="1:22">
       <c r="A7" s="3"/>
-      <c r="B7" s="3">
+      <c r="B7" t="n" s="3">
         <v>201</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="C7" t="str" s="3">
+        <v>渡口行装</v>
+      </c>
+      <c r="D7" t="str" s="3">
+        <v>时装</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" t="str" s="4">
+        <v>云纹织就法袍，衣袂之间灵光流转。</v>
+      </c>
+      <c r="H7" t="str" s="4">
+        <v>完成支线“踏查·水镜滩”获得激活道具</v>
+      </c>
+      <c r="I7" t="n" s="3">
         <v>12904002</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="3">
-        <v>12904002</v>
-      </c>
-      <c r="J7" s="3">
+      <c r="J7" t="n" s="3">
         <v>1</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
-      <c r="N7" s="3">
+      <c r="N7" t="n" s="3">
         <v>10000</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P7" s="3">
-        <v>120</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R7" s="3">
-        <v>100</v>
+      <c r="O7" t="str" s="3">
+        <v>生命值</v>
+      </c>
+      <c r="P7" t="n" s="3">
+        <v>20</v>
+      </c>
+      <c r="Q7" t="str" s="3">
+        <v>基础修为增幅</v>
+      </c>
+      <c r="R7" t="n" s="3">
+        <v>25</v>
       </c>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通用</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="64" customHeight="1" spans="1:22">
       <c r="A8" s="3"/>
-      <c r="B8" s="3">
+      <c r="B8" t="n" s="3">
         <v>301</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="C8" t="str" s="3">
+        <v>青霄灵鹿</v>
+      </c>
+      <c r="D8" t="str" s="3">
+        <v>坐骑</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" t="str" s="4">
+        <v>灵鹿踏云而至，玉角映青光，随你遍览山河。</v>
+      </c>
+      <c r="H8" t="str" s="4">
+        <v>完成合体支线“踏查·霁台”获得激活道具</v>
+      </c>
+      <c r="I8" t="n" s="3">
         <v>12904003</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="3">
-        <v>12904003</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" t="n" s="3">
         <v>1</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
-      <c r="N8" s="3">
+      <c r="N8" t="n" s="3">
         <v>10000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P8" s="3">
-        <v>140</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R8" s="3">
-        <v>100</v>
+      <c r="O8" t="str" s="3">
+        <v>生命值</v>
+      </c>
+      <c r="P8" t="n" s="3">
+        <v>20</v>
+      </c>
+      <c r="Q8" t="str" s="3">
+        <v>基础修为增幅</v>
+      </c>
+      <c r="R8" t="n" s="3">
+        <v>25</v>
       </c>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通用</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="3">
+        <v>302</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">赤鬃追风</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">坐骑</t>
+        </is>
+      </c>
+      <c r="F9" s="3">
+        <v>110001</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">赤鬃如火，金鞍映日，踏风驰骋山河。</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N9" s="3">
+        <v>10000</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通用</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="3">
+        <v>303</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">碧玉流云</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">坐骑</t>
+        </is>
+      </c>
+      <c r="F10" s="3">
+        <v>110002</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">碧玉饰鞍，流苏轻扬，载一身清风入云。</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N10" s="3">
+        <v>10000</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通用</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3">
+        <v>304</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">幽蓝冥驹</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">坐骑</t>
+        </is>
+      </c>
+      <c r="F11" s="3">
+        <v>110003</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">幽焰缠蹄，玄甲凝霜，踏破长夜而来。</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N11" s="3">
+        <v>10000</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通用</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="3">
+        <v>305</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">霜蹄踏雪</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">坐骑</t>
+        </is>
+      </c>
+      <c r="F12" s="3">
+        <v>110004</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">霜甲映雪，银鬃逐月，蹄落处寒光流转。</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N12" s="3">
+        <v>10000</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通用</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="3">
+        <v>306</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金麟曜日</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">坐骑</t>
+        </is>
+      </c>
+      <c r="F13" s="3">
+        <v>110005</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金麟覆甲，赤绶迎风，昂首如曜日临空。</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N13" s="3">
+        <v>10000</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">通用</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3">
+        <v>202</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">青冥剑君</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时装</t>
+        </is>
+      </c>
+      <c r="F14" s="3">
+        <v>10003</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N14" s="3">
+        <v>10000</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">男</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3">
+        <v>203</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">凌霄羽客</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时装</t>
+        </is>
+      </c>
+      <c r="F15" s="3">
+        <v>10004</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">男</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3">
+        <v>204</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">书剑华服</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时装</t>
+        </is>
+      </c>
+      <c r="F16" s="3">
+        <v>10005</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N16" s="3">
+        <v>10000</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">男</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3">
+        <v>205</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">青冥剑仙</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时装</t>
+        </is>
+      </c>
+      <c r="F17" s="3">
+        <v>10006</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N17" s="3">
+        <v>10000</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">女</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3">
+        <v>206</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">寒锋仙子</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时装</t>
+        </is>
+      </c>
+      <c r="F18" s="3">
+        <v>10007</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N18" s="3">
+        <v>10000</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">女</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3">
+        <v>207</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">月白剑使</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">时装</t>
+        </is>
+      </c>
+      <c r="F19" s="3">
+        <v>10008</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N19" s="3">
+        <v>10000</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">女</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1801,4 +2420,144 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="64" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="40" customHeight="1">
+      <x:c r="A1" s="14" t="str">
+        <x:v>项目</x:v>
+      </x:c>
+      <x:c r="B1" s="14" t="str">
+        <x:v>说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="28" customHeight="1">
+      <x:c r="A2" s="12" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>完整内容草案，待用户审核；数值可调；非上线验收</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="263" customHeight="1">
+      <x:c r="A3" s="12" t="str">
+        <x:v>本轮工作</x:v>
+      </x:c>
+      <x:c r="B3" s="12" t="str">
+        <x:v>只使用源表已有四个类别条目与激活道具，补全名称、任务来源与激活收益：1岱舆纪行/头像、101太虚问道/称号、201渡口行装/时装、301青霄灵鹿/坐骑。道具12904000–12904003的功能映射分别指1/101/201/301，主物品组负责回填W表。来源分别是炼气垂练岩支线、大乘回望所来主线、炼气水镜滩支线、合体霁台支线。
+每件至少一组有效激活物品，数量1；所有属性收益归玩家角色，激活后永久生效，与显示/穿戴无关。四件各生命+20、基础修为增幅+25万分比，合集+80生命、+1%基础修为，作为小幅收藏收益，不另增主动技能/词条依赖，也不叠出超额命中等无依据属性。具体总量可由用户后续调。
+资源空值遵循源schema允许空：头像只用图标，称号须真实文字模型及overhead挂点，时装须完整人物模型，坐骑须完整坐骑模型。缺失资源不能用另一类别模型冒充。附资源需求记录源合法预览与待制作清单；通过表结构不等于正式展示验收，激活物品行为与预览/使用仍待程序确认。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="12" t="str">
+        <x:v>交付边界</x:v>
+      </x:c>
+      <x:c r="B4" s="12" t="str">
+        <x:v>源文件未改；坐标/资源/程序挂接按需求清单另验收</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="12" t="str">
+        <x:v>详细说明</x:v>
+      </x:c>
+      <x:c r="B5" s="12" t="str">
+        <x:v>世界09_幻化来源_奖励及资源.md</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="40" customHeight="1">
+      <x:c r="A1" s="19" t="str">
+        <x:v>幻化ID</x:v>
+      </x:c>
+      <x:c r="B1" s="19" t="str">
+        <x:v>分类</x:v>
+      </x:c>
+      <x:c r="C1" s="19" t="str">
+        <x:v>必须制作/核验</x:v>
+      </x:c>
+      <x:c r="D1" s="19" t="str">
+        <x:v>上线验收</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="38" customHeight="1">
+      <x:c r="A2" s="17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="17" t="str">
+        <x:v>头像</x:v>
+      </x:c>
+      <x:c r="C2" s="17" t="str">
+        <x:v>岱舆纪行正式头像贴图；图标尚待制作，12904000是激活物品ID而非图标ID；实际icon_id留空</x:v>
+      </x:c>
+      <x:c r="D2" s="17" t="str">
+        <x:v>列表/预览/角色头像一致</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="28" customHeight="1">
+      <x:c r="A3" s="17" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B3" s="17" t="str">
+        <x:v>称号</x:v>
+      </x:c>
+      <x:c r="C3" s="17" t="str">
+        <x:v>太虚问道文字模型、overhead挂点、无遮挡大小</x:v>
+      </x:c>
+      <x:c r="D3" s="17" t="str">
+        <x:v>独立预览、角色挂接与隐藏</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="28" customHeight="1">
+      <x:c r="A4" s="17" t="n">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B4" s="17" t="str">
+        <x:v>时装</x:v>
+      </x:c>
+      <x:c r="C4" s="17" t="str">
+        <x:v>渡口行装完整人物模型/动作，勿用称号或坐骑模型</x:v>
+      </x:c>
+      <x:c r="D4" s="17" t="str">
+        <x:v>换装后碰撞/攻击/血条不变</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="17" t="n">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B5" s="17" t="str">
+        <x:v>坐骑</x:v>
+      </x:c>
+      <x:c r="C5" s="17" t="str">
+        <x:v>青霄灵鹿完整坐骑模型/动作</x:v>
+      </x:c>
+      <x:c r="D5" s="17" t="str">
+        <x:v>只改外观，不点击即骑乘；奖励归玩家</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>